--- a/pensum/ol20/LOM_Ovingsark_OrgLedelse_kap20_Arbeidstid_og_overtid_NY.xlsx
+++ b/pensum/ol20/LOM_Ovingsark_OrgLedelse_kap20_Arbeidstid_og_overtid_NY.xlsx
@@ -611,6 +611,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -690,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -838,6 +840,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
@@ -852,6 +855,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -913,7 +917,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2 · Arbeidsavtalen til Sara</t>
+          <t>2 · Arbeidsavtalen til den nye lærlingen</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -995,6 +999,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
@@ -1023,6 +1028,7 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
@@ -1082,6 +1088,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1205,6 +1212,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -1445,6 +1453,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -1538,6 +1547,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -1578,6 +1588,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
@@ -1643,6 +1654,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1723,6 +1735,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -1905,6 +1918,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -1982,6 +1996,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -2052,6 +2067,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
@@ -2102,6 +2118,7 @@
         <v/>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -2142,6 +2159,7 @@
         <v/>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
@@ -2149,6 +2167,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -2207,6 +2226,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2229,6 +2249,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -2298,6 +2319,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -2423,6 +2445,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -2474,6 +2497,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
@@ -2481,6 +2505,8 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -2521,6 +2547,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -2579,6 +2606,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2628,6 +2656,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -2733,6 +2762,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -2826,6 +2856,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -2859,6 +2890,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -2866,6 +2898,8 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -2906,6 +2940,7 @@
         <v/>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -2966,6 +3001,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3157,6 +3193,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -3307,6 +3345,8 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -3452,6 +3492,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -3480,6 +3521,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -3531,6 +3573,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -3596,6 +3639,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3684,6 +3728,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -3924,6 +3969,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
@@ -3946,6 +3992,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>

--- a/pensum/ol20/LOM_Ovingsark_OrgLedelse_kap20_Arbeidstid_og_overtid_NY.xlsx
+++ b/pensum/ol20/LOM_Ovingsark_OrgLedelse_kap20_Arbeidstid_og_overtid_NY.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">Hva tjener montøren i måneden, før skatt?</t>
   </si>
   <si>
-    <t xml:space="preserve">40 000 kroner er eksempelet fra Økonomistyring for LØM-emnet, tabell 2.4.</t>
+    <t xml:space="preserve">40 000 kroner er beløpet i oppgave 6, kapittel 2 i Økonomistyring for LØM-emnet. Satsene står i tabell 2.4.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvor mange timer i uka er avtalt?</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3. Hva må timeprisen (B10) være for at en overtidstime skal gi like mye igjen som en vanlig time gjør i dag?</t>
   </si>
   <si>
-    <t xml:space="preserve">Månedslønnen og påslagene er fra Økonomistyring for LØM-emnet, tabell 2.4, slik regnearket bruker dem. Timeprisen 890 kroner er Nordlys Elektro AS sin (faktaarket). Overtidstillegget: arbeidsmiljøloven § 10-6. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Månedslønnen er fra oppgave 6 og påslagene fra tabell 2.4, begge i kapittel 2 i Økonomistyring for LØM-emnet. Timeprisen 890 kroner er Nordlys Elektro AS sin (faktaarket). Overtidstillegget: arbeidsmiljøloven § 10-6. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Arbeidstid, overtid og feriepenger</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">KONSTRUERT FOR UNDERVISNINGEN: timetallene i eksempeluka. Månedslønnen er</t>
   </si>
   <si>
-    <t xml:space="preserve">illustrasjonsbeløpet fra Økonomistyring for LØM-emnet tabell 2.4, timeprisen og</t>
+    <t xml:space="preserve">beløpet i oppgave 6 og satsene i tabell 2.4 i Økonomistyring for LØM-emnet, timeprisen og</t>
   </si>
   <si>
     <t xml:space="preserve">bemanningen er Nordlys Elektro AS' egne, og satsene for feriepenger og</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">Brutto månedslønn</t>
   </si>
   <si>
-    <t xml:space="preserve">Illustrasjonsbeløpet i Økonomistyring for LØM-emnet, tabell 2.4.</t>
+    <t xml:space="preserve">Beløpet i oppgave 6, kapittel 2 i Økonomistyring for LØM-emnet. Satsene står i tabell 2.4.</t>
   </si>
   <si>
     <t xml:space="preserve">Uker i året</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">Fem timer overtid. Vanlig i en travel periode.</t>
   </si>
   <si>
-    <t xml:space="preserve">Taket for samlet arbeidstid i løpet av sju dager.</t>
+    <t xml:space="preserve">Taket for samlet arbeidstid i løpet av sju dager. Grensen kan gjennomsnittsberegnes over åtte uker (§ 10-6 åttende ledd).</t>
   </si>
   <si>
     <t xml:space="preserve">Uka til Ronnys lag. Over taket, og over overtidsgrensen.</t>
@@ -2674,8 +2674,8 @@
         <v>150</v>
       </c>
       <c r="F31" s="29" t="str">
-        <f aca="false">IF(B30&gt;$B$9,"BRUDD på samlet arbeidstid i døgnet (§ 10-6).",IF(B23&gt;$B$10,"BRUDD på samlet arbeidstid i uka (§ 10-6).",IF(B28&gt;$B$12,"BRUDD på overtidsgrensen for sju dager (§ 10-6). Grensen er "&amp;$B$12&amp;" timer uten avtale.","Uka er innenfor grensene i arbeidsmiljøloven kapittel 10.")))</f>
-        <v>BRUDD på samlet arbeidstid i uka (§ 10-6).</v>
+        <f aca="false">IF(B30&gt;$B$9,"BRUDD på samlet arbeidstid i døgnet (§ 10-6).",IF(B23&gt;$B$10,"Over 48 timer denne uka. Lovlig bare hvis snittet over åtte uker er høyst 48 (§ 10-6 åttende ledd).",IF(B28&gt;$B$12,"BRUDD på overtidsgrensen for sju dager (§ 10-6). Grensen er "&amp;$B$12&amp;" timer uten avtale.","Uka er innenfor grensene i arbeidsmiljøloven kapittel 10.")))</f>
+        <v>Over 48 timer denne uka. Lovlig bare hvis snittet over åtte uker er høyst 48 (§ 10-6 åttende ledd).</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4647,7 +4647,7 @@
         <v>150</v>
       </c>
       <c r="F26" s="29" t="str">
-        <f aca="false">IF(MAX(B16:B22)&gt;$B$9,"BRUDD på samlet arbeidstid i døgnet (§ 10-6).",IF(B23&gt;$B$10,"BRUDD på samlet arbeidstid i uka (§ 10-6).",IF(B25&gt;$B$12,"BRUDD på overtidsgrensen for sju dager (§ 10-6).","Uka er innenfor grensene i arbeidsmiljøloven kapittel 10.")))</f>
+        <f aca="false">IF(MAX(B16:B22)&gt;$B$9,"BRUDD på samlet arbeidstid i døgnet (§ 10-6).",IF(B23&gt;$B$10,"Over 48 timer denne uka. Lovlig bare hvis snittet over åtte uker er høyst 48 (§ 10-6 åttende ledd).",IF(B25&gt;$B$12,"BRUDD på overtidsgrensen for sju dager (§ 10-6).","Uka er innenfor grensene i arbeidsmiljøloven kapittel 10.")))</f>
         <v>Uka er innenfor grensene i arbeidsmiljøloven kapittel 10.</v>
       </c>
     </row>
